--- a/data/publications/handbook-statistics-on-indian-economy/annual-series/national-income-saving-employment/Sector-Wise Domestic Savings (At Current Prices).xlsx
+++ b/data/publications/handbook-statistics-on-indian-economy/annual-series/national-income-saving-employment/Sector-Wise Domestic Savings (At Current Prices).xlsx
@@ -3,13 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="Old Items" sheetId="1" r:id="rId1"/>
-    <sheet name="New Items" sheetId="2" r:id="rId2"/>
+    <sheet name="Base Year � 2011-2012" sheetId="2" r:id="rId2"/>
+    <sheet name="Base Year � 2022-2023" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="109">
   <si>
     <t>Year</t>
   </si>
@@ -281,16 +282,16 @@
     <t>1.4 Household sector</t>
   </si>
   <si>
-    <t>1.4.1.1 Gross financial saving</t>
-  </si>
-  <si>
-    <t>1.4.1.2 Less financial liabilities</t>
-  </si>
-  <si>
-    <t>1.4.2 Saving in physical assets</t>
-  </si>
-  <si>
-    <t>1.4.3 Saving in the form of gold and silver ornaments</t>
+    <t>1.4.1 Gross financial saving</t>
+  </si>
+  <si>
+    <t>1.4.2 Less financial liabilities</t>
+  </si>
+  <si>
+    <t>1.4.3 Saving in physical assets</t>
+  </si>
+  <si>
+    <t>1.4.4 Saving in the form of gold and silver ornaments</t>
   </si>
   <si>
     <t xml:space="preserve">2023-24   </t>
@@ -329,8 +330,18 @@
     <t>Base Year : 2011-2012</t>
   </si>
   <si>
+    <t xml:space="preserve">Note     : Gross financial saving &amp; liabilities for household sector includes gross financial savings &amp; liabilities for quasi corporate sector.
+Source : National Statistics Office (NSO).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-25   </t>
+  </si>
+  <si>
+    <t>Base Year : 2022-2023</t>
+  </si>
+  <si>
     <t xml:space="preserve">Note : Gross financial saving &amp; liabilities for household sector includes gross financial savings &amp; liabilities for quasi corporate sector.
-Source : National Statistical Office (NSO).</t>
+Source : National Statistics Office (NSO).</t>
   </si>
 </sst>
 </file>
@@ -3208,4 +3219,346 @@
   <pageSetup paperSize="120" scale="100" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:R14"/>
+  <cols>
+    <col min="1" max="1" width="4.67767866666667" customWidth="1"/>
+    <col min="2" max="2" width="15.4582386666667" customWidth="1"/>
+    <col min="3" max="7" width="20.8466173333333" customWidth="1"/>
+    <col min="8" max="8" width="20.8542226666667" customWidth="1"/>
+    <col min="9" max="9" width="20.839012" customWidth="1"/>
+    <col min="10" max="19" width="20.8466173333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
+    <row r="2" s="1" customFormat="1" ht="15.999" customHeight="1">
+      <c r="B2" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
+    <row r="4" s="1" customFormat="1" ht="14.3991" customHeight="1">
+      <c r="B4" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="12"/>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
+    <row r="6" s="1" customFormat="1" ht="14.3991" customHeight="1">
+      <c r="B6" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="12"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="6.9329" customHeight="1"/>
+    <row r="8" s="1" customFormat="1" ht="35.1978" customHeight="1">
+      <c r="B8" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="N8" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="O8" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="P8" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q8" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="R8" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="S8" s="15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="14.3991" customHeight="1">
+      <c r="B9" s="16">
+        <v>1</v>
+      </c>
+      <c r="C9" s="17">
+        <v>2</v>
+      </c>
+      <c r="D9" s="17">
+        <v>3</v>
+      </c>
+      <c r="E9" s="17">
+        <v>4</v>
+      </c>
+      <c r="F9" s="17">
+        <v>5</v>
+      </c>
+      <c r="G9" s="17">
+        <v>6</v>
+      </c>
+      <c r="H9" s="17">
+        <v>7</v>
+      </c>
+      <c r="I9" s="17">
+        <v>8</v>
+      </c>
+      <c r="J9" s="17">
+        <v>9</v>
+      </c>
+      <c r="K9" s="17">
+        <v>10</v>
+      </c>
+      <c r="L9" s="17">
+        <v>11</v>
+      </c>
+      <c r="M9" s="17">
+        <v>12</v>
+      </c>
+      <c r="N9" s="17">
+        <v>13</v>
+      </c>
+      <c r="O9" s="17">
+        <v>14</v>
+      </c>
+      <c r="P9" s="17">
+        <v>15</v>
+      </c>
+      <c r="Q9" s="17">
+        <v>16</v>
+      </c>
+      <c r="R9" s="17">
+        <v>17</v>
+      </c>
+      <c r="S9" s="17">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="14.3991" customHeight="1">
+      <c r="B10" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="18">
+        <v>11.1133241970121e6</v>
+      </c>
+      <c r="D10" s="18">
+        <v>3.20712770649141e6</v>
+      </c>
+      <c r="E10" s="18">
+        <v>472146.636487172</v>
+      </c>
+      <c r="F10" s="18">
+        <v>68023.2652289804</v>
+      </c>
+      <c r="G10" s="18">
+        <v>404123.371258191</v>
+      </c>
+      <c r="H10" s="18">
+        <v>2.73498107000424e6</v>
+      </c>
+      <c r="I10" s="18">
+        <v>1.10990002680757e6</v>
+      </c>
+      <c r="J10" s="18">
+        <v>590172.4239</v>
+      </c>
+      <c r="K10" s="18">
+        <v>2760.9</v>
+      </c>
+      <c r="L10" s="18">
+        <v>587411.5239</v>
+      </c>
+      <c r="M10" s="18">
+        <v>519727.60290757</v>
+      </c>
+      <c r="N10" s="18">
+        <v>-104305.111176923</v>
+      </c>
+      <c r="O10" s="18">
+        <v>6.90060157489001e6</v>
+      </c>
+      <c r="P10" s="18">
+        <v>3.82836125275483e6</v>
+      </c>
+      <c r="Q10" s="18">
+        <v>1.5712423221408e6</v>
+      </c>
+      <c r="R10" s="18">
+        <v>4.42512599709015e6</v>
+      </c>
+      <c r="S10" s="18">
+        <v>218356.647185821</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="14.3991" customHeight="1">
+      <c r="B11" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="19">
+        <v>9.51745040924909e6</v>
+      </c>
+      <c r="D11" s="19">
+        <v>2.88042942587349e6</v>
+      </c>
+      <c r="E11" s="19">
+        <v>465393.586986493</v>
+      </c>
+      <c r="F11" s="19">
+        <v>66297.5703671008</v>
+      </c>
+      <c r="G11" s="19">
+        <v>399096.016619392</v>
+      </c>
+      <c r="H11" s="19">
+        <v>2.415035838887e6</v>
+      </c>
+      <c r="I11" s="19">
+        <v>993641.418726163</v>
+      </c>
+      <c r="J11" s="19">
+        <v>535509.8992</v>
+      </c>
+      <c r="K11" s="19">
+        <v>2580.42</v>
+      </c>
+      <c r="L11" s="19">
+        <v>532929.4792</v>
+      </c>
+      <c r="M11" s="19">
+        <v>458131.519526163</v>
+      </c>
+      <c r="N11" s="19">
+        <v>-320170.64432567</v>
+      </c>
+      <c r="O11" s="19">
+        <v>5.9635502089751e6</v>
+      </c>
+      <c r="P11" s="19">
+        <v>3.57565741606532e6</v>
+      </c>
+      <c r="Q11" s="19">
+        <v>1.87900020051279e6</v>
+      </c>
+      <c r="R11" s="19">
+        <v>4.09476642581166e6</v>
+      </c>
+      <c r="S11" s="19">
+        <v>172126.567610912</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="14.3991" customHeight="1">
+      <c r="B12" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="20">
+        <v>7.77291749970453e6</v>
+      </c>
+      <c r="D12" s="20">
+        <v>2.25996166034376e6</v>
+      </c>
+      <c r="E12" s="20">
+        <v>346284.768926408</v>
+      </c>
+      <c r="F12" s="20">
+        <v>60990.1672052918</v>
+      </c>
+      <c r="G12" s="20">
+        <v>285294.601721117</v>
+      </c>
+      <c r="H12" s="20">
+        <v>1.91367689141735e6</v>
+      </c>
+      <c r="I12" s="20">
+        <v>879103.397610696</v>
+      </c>
+      <c r="J12" s="20">
+        <v>459701.4761869</v>
+      </c>
+      <c r="K12" s="20">
+        <v>2725.28</v>
+      </c>
+      <c r="L12" s="20">
+        <v>456976.1961869</v>
+      </c>
+      <c r="M12" s="20">
+        <v>419401.921423796</v>
+      </c>
+      <c r="N12" s="20">
+        <v>-591584.899265436</v>
+      </c>
+      <c r="O12" s="20">
+        <v>5.22543734101552e6</v>
+      </c>
+      <c r="P12" s="20">
+        <v>2.98227946539692e6</v>
+      </c>
+      <c r="Q12" s="20">
+        <v>1.59648348395118e6</v>
+      </c>
+      <c r="R12" s="20">
+        <v>3.67463509693499e6</v>
+      </c>
+      <c r="S12" s="20">
+        <v>165006.262634782</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
+    <row r="14" s="1" customFormat="1" ht="31.4647" customHeight="1">
+      <c r="B14" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
+  </mergeCells>
+  <pageSetup paperSize="120" scale="100" orientation="landscape"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
 </file>